--- a/Methanol/Südafrika_Methanol_5_Bio_H2_Methanolreaktor_Brownfield/Datenbank.xlsx
+++ b/Methanol/Südafrika_Methanol_5_Bio_H2_Methanolreaktor_Brownfield/Datenbank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Methanol\Südafrika_Methanol_5_Bio_H2_Methanolreaktor_Brownfield\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72A4C339-E6EB-46F8-9A39-553E1F4DD492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B47302E-B90C-451E-A636-463E05562A6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-4455" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-6945" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="395">
   <si>
     <t>PEM Elektrolyse</t>
   </si>
@@ -1361,6 +1361,12 @@
   </si>
   <si>
     <t>kg</t>
+  </si>
+  <si>
+    <t>Landesspezifischer Zinssatz</t>
+  </si>
+  <si>
+    <t>wacc_change</t>
   </si>
 </sst>
 </file>
@@ -1634,13 +1640,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1649,20 +1649,26 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -2005,23 +2011,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G77"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G78"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="36.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.90625" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="36.1796875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="40.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.77734375" customWidth="1"/>
-    <col min="9" max="9" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.81640625" customWidth="1"/>
+    <col min="9" max="9" width="13.90625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>69</v>
       </c>
@@ -2042,7 +2048,7 @@
       </c>
       <c r="G1" s="5"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="58" t="s">
         <v>70</v>
       </c>
@@ -2062,7 +2068,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="59"/>
       <c r="B3" s="66"/>
       <c r="C3" t="s">
@@ -2078,7 +2084,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="59"/>
       <c r="B4" s="66"/>
       <c r="C4" t="s">
@@ -2094,7 +2100,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="59"/>
       <c r="B5" s="66"/>
       <c r="C5" t="s">
@@ -2110,7 +2116,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="59"/>
       <c r="B6" s="66"/>
       <c r="C6" t="s">
@@ -2126,7 +2132,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="59"/>
       <c r="B7" s="66"/>
       <c r="C7" t="s">
@@ -2142,7 +2148,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="59"/>
       <c r="B8" s="69" t="s">
         <v>227</v>
@@ -2160,7 +2166,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="59"/>
       <c r="B9" s="66"/>
       <c r="C9" t="s">
@@ -2176,7 +2182,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="59"/>
       <c r="B10" s="66"/>
       <c r="C10" s="33" t="s">
@@ -2192,7 +2198,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="59"/>
       <c r="B11" s="66"/>
       <c r="C11" s="33" t="s">
@@ -2209,7 +2215,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="59"/>
       <c r="B12" s="66"/>
       <c r="C12" t="s">
@@ -2225,7 +2231,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="59"/>
       <c r="B13" s="66"/>
       <c r="C13" t="s">
@@ -2241,7 +2247,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="59"/>
       <c r="B14" s="66"/>
       <c r="C14" t="s">
@@ -2257,7 +2263,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="59"/>
       <c r="B15" s="70"/>
       <c r="C15" s="14" t="s">
@@ -2273,7 +2279,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="59"/>
       <c r="B16" s="69" t="s">
         <v>269</v>
@@ -2291,7 +2297,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="59"/>
       <c r="B17" s="66"/>
       <c r="C17" t="s">
@@ -2307,7 +2313,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="59"/>
       <c r="B18" s="66"/>
       <c r="C18" t="s">
@@ -2323,7 +2329,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="59"/>
       <c r="B19" s="66"/>
       <c r="C19" t="s">
@@ -2339,7 +2345,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="59"/>
       <c r="B20" s="66"/>
       <c r="C20" t="s">
@@ -2355,7 +2361,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="59"/>
       <c r="B21" s="70"/>
       <c r="C21" s="14" t="s">
@@ -2371,7 +2377,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="59"/>
       <c r="B22" s="62" t="s">
         <v>336</v>
@@ -2389,7 +2395,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="59"/>
       <c r="B23" s="62"/>
       <c r="C23" t="s">
@@ -2405,7 +2411,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="59"/>
       <c r="B24" s="62"/>
       <c r="C24" t="s">
@@ -2421,7 +2427,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="59"/>
       <c r="B25" s="62"/>
       <c r="C25" t="s">
@@ -2437,7 +2443,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="59"/>
       <c r="B26" s="62"/>
       <c r="C26" t="s">
@@ -2453,7 +2459,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="59"/>
       <c r="B27" s="62"/>
       <c r="C27" t="s">
@@ -2469,7 +2475,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="59"/>
       <c r="B28" s="62"/>
       <c r="C28" t="s">
@@ -2485,7 +2491,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="59"/>
       <c r="B29" s="62"/>
       <c r="C29" t="s">
@@ -2501,7 +2507,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="59"/>
       <c r="B30" s="62"/>
       <c r="C30" t="s">
@@ -2517,7 +2523,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="58" t="s">
         <v>71</v>
       </c>
@@ -2537,7 +2543,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="59"/>
       <c r="B32" s="62"/>
       <c r="C32" t="s">
@@ -2553,7 +2559,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="59"/>
       <c r="B33" s="62"/>
       <c r="C33" t="s">
@@ -2569,7 +2575,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="59"/>
       <c r="B34" s="62"/>
       <c r="C34" t="s">
@@ -2585,7 +2591,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="59"/>
       <c r="B35" s="62"/>
       <c r="C35" t="s">
@@ -2601,7 +2607,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="59"/>
       <c r="B36" s="62"/>
       <c r="C36" t="s">
@@ -2617,7 +2623,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="59"/>
       <c r="B37" s="62"/>
       <c r="C37" t="s">
@@ -2633,7 +2639,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="59"/>
       <c r="B38" s="63"/>
       <c r="C38" s="14" t="s">
@@ -2649,7 +2655,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="59"/>
       <c r="B39" s="64" t="s">
         <v>311</v>
@@ -2667,7 +2673,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="59"/>
       <c r="B40" s="62"/>
       <c r="C40" t="s">
@@ -2683,7 +2689,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="59"/>
       <c r="B41" s="62"/>
       <c r="C41" t="s">
@@ -2699,7 +2705,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="59"/>
       <c r="B42" s="62"/>
       <c r="C42" t="s">
@@ -2715,7 +2721,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="59"/>
       <c r="B43" s="62"/>
       <c r="C43" t="s">
@@ -2731,7 +2737,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="59"/>
       <c r="B44" s="62"/>
       <c r="C44" t="s">
@@ -2747,7 +2753,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="59"/>
       <c r="B45" s="62"/>
       <c r="C45" t="s">
@@ -2763,7 +2769,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="59"/>
       <c r="B46" s="62"/>
       <c r="C46" s="14" t="s">
@@ -2779,7 +2785,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="59"/>
       <c r="B47" s="64" t="s">
         <v>201</v>
@@ -2797,7 +2803,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="59"/>
       <c r="B48" s="66"/>
       <c r="C48" t="s">
@@ -2814,7 +2820,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="59"/>
       <c r="B49" s="66"/>
       <c r="C49" t="s">
@@ -2830,7 +2836,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="59"/>
       <c r="B50" s="66"/>
       <c r="C50" t="s">
@@ -2846,7 +2852,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="59"/>
       <c r="B51" s="66"/>
       <c r="C51" t="s">
@@ -2862,7 +2868,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="59"/>
       <c r="B52" s="66"/>
       <c r="C52" t="s">
@@ -2878,7 +2884,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="59"/>
       <c r="B53" s="66"/>
       <c r="C53" t="s">
@@ -2894,7 +2900,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="59"/>
       <c r="B54" s="66"/>
       <c r="C54" t="s">
@@ -2910,7 +2916,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="59"/>
       <c r="B55" s="66"/>
       <c r="C55" t="s">
@@ -2926,7 +2932,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A56" s="60"/>
       <c r="B56" s="67"/>
       <c r="C56" s="19" t="s">
@@ -2942,7 +2948,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="58" t="s">
         <v>72</v>
       </c>
@@ -2962,7 +2968,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="59"/>
       <c r="B58" s="24" t="s">
         <v>376</v>
@@ -2980,7 +2986,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="59"/>
       <c r="B59" s="27" t="s">
         <v>337</v>
@@ -2998,7 +3004,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="59"/>
       <c r="B60" s="64" t="s">
         <v>4</v>
@@ -3016,7 +3022,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="59"/>
       <c r="B61" s="62"/>
       <c r="C61" t="s">
@@ -3032,7 +3038,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="59"/>
       <c r="B62" s="62"/>
       <c r="C62" t="s">
@@ -3048,7 +3054,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="59"/>
       <c r="B63" s="62"/>
       <c r="C63" t="s">
@@ -3064,7 +3070,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="59"/>
       <c r="B64" s="62"/>
       <c r="C64" t="s">
@@ -3080,7 +3086,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="59"/>
       <c r="B65" s="62"/>
       <c r="C65" t="s">
@@ -3096,7 +3102,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="59"/>
       <c r="B66" s="63"/>
       <c r="C66" s="14" t="s">
@@ -3112,7 +3118,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="59"/>
       <c r="B67" s="64" t="s">
         <v>5</v>
@@ -3130,7 +3136,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="59"/>
       <c r="B68" s="62"/>
       <c r="C68" t="s">
@@ -3146,7 +3152,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="59"/>
       <c r="B69" s="62"/>
       <c r="C69" t="s">
@@ -3162,7 +3168,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="59"/>
       <c r="B70" s="62"/>
       <c r="C70" t="s">
@@ -3178,7 +3184,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="59"/>
       <c r="B71" s="62"/>
       <c r="C71" t="s">
@@ -3194,7 +3200,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="59"/>
       <c r="B72" s="62"/>
       <c r="C72" t="s">
@@ -3210,7 +3216,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="60"/>
       <c r="B73" s="65"/>
       <c r="C73" s="19" t="s">
@@ -3226,7 +3232,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" s="58" t="s">
         <v>76</v>
       </c>
@@ -3246,7 +3252,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" s="59"/>
       <c r="B75" s="5" t="s">
         <v>295</v>
@@ -3264,7 +3270,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="59"/>
       <c r="B76" s="32" t="s">
         <v>79</v>
@@ -3282,7 +3288,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A77" s="60"/>
       <c r="B77" s="3" t="s">
         <v>258</v>
@@ -3298,6 +3304,26 @@
       </c>
       <c r="F77" s="19" t="s">
         <v>271</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C78" t="s">
+        <v>393</v>
+      </c>
+      <c r="D78" t="s">
+        <v>394</v>
+      </c>
+      <c r="E78" s="10">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="F78" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3325,18 +3351,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83AB2E79-6F94-41B5-A552-C40EC4890194}">
   <dimension ref="A1:F149"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" style="41" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" style="41" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.5546875" style="41" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="50.77734375" style="41" customWidth="1"/>
-    <col min="5" max="5" width="46.109375" style="41" customWidth="1"/>
-    <col min="6" max="6" width="37.5546875" style="41" customWidth="1"/>
-    <col min="7" max="16384" width="11.5546875" style="41"/>
+    <col min="1" max="1" width="14.54296875" style="41" customWidth="1"/>
+    <col min="2" max="2" width="30.36328125" style="41" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.54296875" style="41" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.81640625" style="41" customWidth="1"/>
+    <col min="5" max="5" width="46.08984375" style="41" customWidth="1"/>
+    <col min="6" max="6" width="37.54296875" style="41" customWidth="1"/>
+    <col min="7" max="16384" width="11.54296875" style="41"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="38" t="s">
         <v>69</v>
       </c>
@@ -3356,11 +3382,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="74" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="72" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="74" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="42" t="s">
@@ -3374,9 +3400,9 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="75"/>
-      <c r="B3" s="72"/>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="73"/>
+      <c r="B3" s="71"/>
       <c r="C3" s="41" t="s">
         <v>107</v>
       </c>
@@ -3388,9 +3414,9 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="75"/>
-      <c r="B4" s="72"/>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="73"/>
+      <c r="B4" s="71"/>
       <c r="C4" s="41" t="s">
         <v>84</v>
       </c>
@@ -3402,9 +3428,9 @@
         <v>118</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="75"/>
-      <c r="B5" s="72"/>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="73"/>
+      <c r="B5" s="71"/>
       <c r="C5" s="41" t="s">
         <v>138</v>
       </c>
@@ -3416,9 +3442,9 @@
         <v>132</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="75"/>
-      <c r="B6" s="72"/>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="73"/>
+      <c r="B6" s="71"/>
       <c r="C6" s="41" t="s">
         <v>141</v>
       </c>
@@ -3430,9 +3456,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="75"/>
-      <c r="B7" s="72"/>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="73"/>
+      <c r="B7" s="71"/>
       <c r="C7" s="41" t="s">
         <v>155</v>
       </c>
@@ -3444,9 +3470,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="75"/>
-      <c r="B8" s="72"/>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="73"/>
+      <c r="B8" s="71"/>
       <c r="C8" s="41" t="s">
         <v>196</v>
       </c>
@@ -3458,9 +3484,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="75"/>
-      <c r="B9" s="72"/>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="73"/>
+      <c r="B9" s="71"/>
       <c r="C9" s="41" t="s">
         <v>167</v>
       </c>
@@ -3472,9 +3498,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="75"/>
-      <c r="B10" s="72"/>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="73"/>
+      <c r="B10" s="71"/>
       <c r="C10" s="41" t="s">
         <v>188</v>
       </c>
@@ -3486,14 +3512,14 @@
         <v>149</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="75"/>
-      <c r="B11" s="72"/>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="73"/>
+      <c r="B11" s="71"/>
       <c r="E11" s="46"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="75"/>
-      <c r="B12" s="71" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="73"/>
+      <c r="B12" s="75" t="s">
         <v>227</v>
       </c>
       <c r="C12" s="48" t="s">
@@ -3507,9 +3533,9 @@
         <v>104</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="75"/>
-      <c r="B13" s="72"/>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="73"/>
+      <c r="B13" s="71"/>
       <c r="C13" s="41" t="s">
         <v>251</v>
       </c>
@@ -3521,9 +3547,9 @@
         <v>254</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="75"/>
-      <c r="B14" s="72"/>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="73"/>
+      <c r="B14" s="71"/>
       <c r="C14" s="41" t="s">
         <v>139</v>
       </c>
@@ -3535,9 +3561,9 @@
         <v>132</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="75"/>
-      <c r="B15" s="72"/>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="73"/>
+      <c r="B15" s="71"/>
       <c r="C15" s="41" t="s">
         <v>252</v>
       </c>
@@ -3549,9 +3575,9 @@
         <v>255</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="75"/>
-      <c r="B16" s="72"/>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="73"/>
+      <c r="B16" s="71"/>
       <c r="C16" s="41" t="s">
         <v>84</v>
       </c>
@@ -3563,9 +3589,9 @@
         <v>118</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="75"/>
-      <c r="B17" s="72"/>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="73"/>
+      <c r="B17" s="71"/>
       <c r="C17" s="41" t="s">
         <v>141</v>
       </c>
@@ -3577,9 +3603,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="75"/>
-      <c r="B18" s="72"/>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="73"/>
+      <c r="B18" s="71"/>
       <c r="C18" s="41" t="s">
         <v>155</v>
       </c>
@@ -3591,9 +3617,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="75"/>
-      <c r="B19" s="72"/>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="73"/>
+      <c r="B19" s="71"/>
       <c r="C19" s="41" t="s">
         <v>196</v>
       </c>
@@ -3605,9 +3631,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="75"/>
-      <c r="B20" s="72"/>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="73"/>
+      <c r="B20" s="71"/>
       <c r="C20" s="41" t="s">
         <v>167</v>
       </c>
@@ -3619,9 +3645,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="75"/>
-      <c r="B21" s="72"/>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="73"/>
+      <c r="B21" s="71"/>
       <c r="C21" s="41" t="s">
         <v>188</v>
       </c>
@@ -3633,17 +3659,17 @@
         <v>149</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="75"/>
-      <c r="B22" s="73"/>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="73"/>
+      <c r="B22" s="76"/>
       <c r="C22" s="50"/>
       <c r="D22" s="50"/>
       <c r="E22" s="51"/>
       <c r="F22" s="50"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="75"/>
-      <c r="B23" s="71" t="s">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" s="73"/>
+      <c r="B23" s="75" t="s">
         <v>269</v>
       </c>
       <c r="C23" s="41" t="s">
@@ -3657,9 +3683,9 @@
         <v>289</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="75"/>
-      <c r="B24" s="72"/>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="73"/>
+      <c r="B24" s="71"/>
       <c r="C24" s="41" t="s">
         <v>107</v>
       </c>
@@ -3671,9 +3697,9 @@
         <v>186</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="75"/>
-      <c r="B25" s="72"/>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="73"/>
+      <c r="B25" s="71"/>
       <c r="C25" s="41" t="s">
         <v>84</v>
       </c>
@@ -3685,9 +3711,9 @@
         <v>293</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="75"/>
-      <c r="B26" s="72"/>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="73"/>
+      <c r="B26" s="71"/>
       <c r="C26" s="41" t="s">
         <v>291</v>
       </c>
@@ -3699,9 +3725,9 @@
         <v>290</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="75"/>
-      <c r="B27" s="72"/>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" s="73"/>
+      <c r="B27" s="71"/>
       <c r="C27" s="41" t="s">
         <v>141</v>
       </c>
@@ -3713,9 +3739,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="75"/>
-      <c r="B28" s="72"/>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="73"/>
+      <c r="B28" s="71"/>
       <c r="C28" s="41" t="s">
         <v>155</v>
       </c>
@@ -3727,9 +3753,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="75"/>
-      <c r="B29" s="72"/>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" s="73"/>
+      <c r="B29" s="71"/>
       <c r="C29" s="41" t="s">
         <v>196</v>
       </c>
@@ -3741,9 +3767,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="75"/>
-      <c r="B30" s="72"/>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" s="73"/>
+      <c r="B30" s="71"/>
       <c r="C30" s="41" t="s">
         <v>167</v>
       </c>
@@ -3755,9 +3781,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="75"/>
-      <c r="B31" s="72"/>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" s="73"/>
+      <c r="B31" s="71"/>
       <c r="C31" s="41" t="s">
         <v>188</v>
       </c>
@@ -3769,17 +3795,17 @@
         <v>149</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="75"/>
-      <c r="B32" s="73"/>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" s="73"/>
+      <c r="B32" s="76"/>
       <c r="C32" s="50"/>
       <c r="D32" s="50"/>
       <c r="E32" s="51"/>
       <c r="F32" s="50"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="75"/>
-      <c r="B33" s="79" t="s">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" s="73"/>
+      <c r="B33" s="77" t="s">
         <v>354</v>
       </c>
       <c r="C33" s="41" t="s">
@@ -3793,9 +3819,9 @@
         <v>104</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="75"/>
-      <c r="B34" s="79"/>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" s="73"/>
+      <c r="B34" s="77"/>
       <c r="C34" s="41" t="s">
         <v>107</v>
       </c>
@@ -3807,9 +3833,9 @@
         <v>186</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="75"/>
-      <c r="B35" s="79"/>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" s="73"/>
+      <c r="B35" s="77"/>
       <c r="C35" s="41" t="s">
         <v>84</v>
       </c>
@@ -3821,9 +3847,9 @@
         <v>118</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="75"/>
-      <c r="B36" s="79"/>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" s="73"/>
+      <c r="B36" s="77"/>
       <c r="C36" s="41" t="s">
         <v>279</v>
       </c>
@@ -3835,9 +3861,9 @@
         <v>290</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="75"/>
-      <c r="B37" s="79"/>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" s="73"/>
+      <c r="B37" s="77"/>
       <c r="C37" s="41" t="s">
         <v>366</v>
       </c>
@@ -3849,9 +3875,9 @@
         <v>370</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="75"/>
-      <c r="B38" s="79"/>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" s="73"/>
+      <c r="B38" s="77"/>
       <c r="C38" s="41" t="s">
         <v>256</v>
       </c>
@@ -3863,9 +3889,9 @@
         <v>255</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="75"/>
-      <c r="B39" s="79"/>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39" s="73"/>
+      <c r="B39" s="77"/>
       <c r="C39" s="41" t="s">
         <v>141</v>
       </c>
@@ -3877,9 +3903,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="75"/>
-      <c r="B40" s="79"/>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A40" s="73"/>
+      <c r="B40" s="77"/>
       <c r="C40" s="41" t="s">
         <v>155</v>
       </c>
@@ -3891,9 +3917,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="75"/>
-      <c r="B41" s="79"/>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" s="73"/>
+      <c r="B41" s="77"/>
       <c r="C41" s="41" t="s">
         <v>161</v>
       </c>
@@ -3905,9 +3931,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="75"/>
-      <c r="B42" s="79"/>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A42" s="73"/>
+      <c r="B42" s="77"/>
       <c r="C42" s="41" t="s">
         <v>196</v>
       </c>
@@ -3919,9 +3945,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="75"/>
-      <c r="B43" s="79"/>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43" s="73"/>
+      <c r="B43" s="77"/>
       <c r="C43" s="41" t="s">
         <v>167</v>
       </c>
@@ -3933,9 +3959,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="75"/>
-      <c r="B44" s="79"/>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" s="73"/>
+      <c r="B44" s="77"/>
       <c r="C44" s="41" t="s">
         <v>188</v>
       </c>
@@ -3947,13 +3973,13 @@
         <v>149</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="75"/>
-      <c r="B45" s="79"/>
+    <row r="45" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="73"/>
+      <c r="B45" s="77"/>
       <c r="E45" s="46"/>
     </row>
-    <row r="46" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="74" t="s">
+    <row r="46" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="72" t="s">
         <v>71</v>
       </c>
       <c r="B46" s="81" t="s">
@@ -3970,9 +3996,9 @@
         <v>391</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="75"/>
-      <c r="B47" s="79"/>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" s="73"/>
+      <c r="B47" s="77"/>
       <c r="C47" s="41" t="s">
         <v>111</v>
       </c>
@@ -3984,9 +4010,9 @@
         <v>392</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="75"/>
-      <c r="B48" s="79"/>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A48" s="73"/>
+      <c r="B48" s="77"/>
       <c r="C48" s="41" t="s">
         <v>135</v>
       </c>
@@ -3998,9 +4024,9 @@
         <v>132</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="75"/>
-      <c r="B49" s="79"/>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49" s="73"/>
+      <c r="B49" s="77"/>
       <c r="C49" s="41" t="s">
         <v>136</v>
       </c>
@@ -4012,9 +4038,9 @@
         <v>132</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="75"/>
-      <c r="B50" s="79"/>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A50" s="73"/>
+      <c r="B50" s="77"/>
       <c r="C50" s="41" t="s">
         <v>141</v>
       </c>
@@ -4026,9 +4052,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="75"/>
-      <c r="B51" s="79"/>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A51" s="73"/>
+      <c r="B51" s="77"/>
       <c r="C51" s="41" t="s">
         <v>155</v>
       </c>
@@ -4040,9 +4066,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="75"/>
-      <c r="B52" s="79"/>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A52" s="73"/>
+      <c r="B52" s="77"/>
       <c r="C52" s="41" t="s">
         <v>196</v>
       </c>
@@ -4054,9 +4080,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="75"/>
-      <c r="B53" s="79"/>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A53" s="73"/>
+      <c r="B53" s="77"/>
       <c r="C53" s="41" t="s">
         <v>167</v>
       </c>
@@ -4068,9 +4094,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="75"/>
-      <c r="B54" s="79"/>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A54" s="73"/>
+      <c r="B54" s="77"/>
       <c r="C54" s="41" t="s">
         <v>188</v>
       </c>
@@ -4082,17 +4108,17 @@
         <v>149</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="75"/>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A55" s="73"/>
       <c r="B55" s="82"/>
       <c r="C55" s="50"/>
       <c r="D55" s="50"/>
       <c r="E55" s="51"/>
       <c r="F55" s="50"/>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="75"/>
-      <c r="B56" s="79" t="s">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A56" s="73"/>
+      <c r="B56" s="77" t="s">
         <v>311</v>
       </c>
       <c r="C56" s="41" t="s">
@@ -4106,9 +4132,9 @@
         <v>334</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="75"/>
-      <c r="B57" s="79"/>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A57" s="73"/>
+      <c r="B57" s="77"/>
       <c r="C57" s="41" t="s">
         <v>111</v>
       </c>
@@ -4120,9 +4146,9 @@
         <v>335</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="75"/>
-      <c r="B58" s="79"/>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A58" s="73"/>
+      <c r="B58" s="77"/>
       <c r="C58" s="41" t="s">
         <v>135</v>
       </c>
@@ -4134,9 +4160,9 @@
         <v>389</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="75"/>
-      <c r="B59" s="79"/>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A59" s="73"/>
+      <c r="B59" s="77"/>
       <c r="C59" s="41" t="s">
         <v>136</v>
       </c>
@@ -4148,9 +4174,9 @@
         <v>389</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="75"/>
-      <c r="B60" s="79"/>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A60" s="73"/>
+      <c r="B60" s="77"/>
       <c r="C60" s="41" t="s">
         <v>141</v>
       </c>
@@ -4162,9 +4188,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="75"/>
-      <c r="B61" s="79"/>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A61" s="73"/>
+      <c r="B61" s="77"/>
       <c r="C61" s="41" t="s">
         <v>155</v>
       </c>
@@ -4176,9 +4202,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="75"/>
-      <c r="B62" s="79"/>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A62" s="73"/>
+      <c r="B62" s="77"/>
       <c r="C62" s="41" t="s">
         <v>196</v>
       </c>
@@ -4190,9 +4216,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="75"/>
-      <c r="B63" s="79"/>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A63" s="73"/>
+      <c r="B63" s="77"/>
       <c r="C63" s="41" t="s">
         <v>167</v>
       </c>
@@ -4204,9 +4230,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="75"/>
-      <c r="B64" s="79"/>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A64" s="73"/>
+      <c r="B64" s="77"/>
       <c r="C64" s="41" t="s">
         <v>188</v>
       </c>
@@ -4218,14 +4244,14 @@
         <v>149</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="75"/>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A65" s="73"/>
       <c r="B65" s="82"/>
       <c r="E65" s="46"/>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="75"/>
-      <c r="B66" s="80" t="s">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A66" s="73"/>
+      <c r="B66" s="79" t="s">
         <v>6</v>
       </c>
       <c r="C66" s="48" t="s">
@@ -4239,9 +4265,9 @@
         <v>98</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="75"/>
-      <c r="B67" s="79"/>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A67" s="73"/>
+      <c r="B67" s="77"/>
       <c r="C67" s="41" t="s">
         <v>113</v>
       </c>
@@ -4253,9 +4279,9 @@
         <v>105</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="75"/>
-      <c r="B68" s="72"/>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A68" s="73"/>
+      <c r="B68" s="71"/>
       <c r="C68" s="41" t="s">
         <v>111</v>
       </c>
@@ -4267,9 +4293,9 @@
         <v>114</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="75"/>
-      <c r="B69" s="72"/>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A69" s="73"/>
+      <c r="B69" s="71"/>
       <c r="C69" s="41" t="s">
         <v>107</v>
       </c>
@@ -4281,9 +4307,9 @@
         <v>66</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="75"/>
-      <c r="B70" s="72"/>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A70" s="73"/>
+      <c r="B70" s="71"/>
       <c r="C70" s="41" t="s">
         <v>126</v>
       </c>
@@ -4295,9 +4321,9 @@
         <v>118</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="75"/>
-      <c r="B71" s="72"/>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A71" s="73"/>
+      <c r="B71" s="71"/>
       <c r="C71" s="41" t="s">
         <v>127</v>
       </c>
@@ -4309,9 +4335,9 @@
         <v>118</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="75"/>
-      <c r="B72" s="72"/>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A72" s="73"/>
+      <c r="B72" s="71"/>
       <c r="C72" s="41" t="s">
         <v>141</v>
       </c>
@@ -4323,9 +4349,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="75"/>
-      <c r="B73" s="72"/>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A73" s="73"/>
+      <c r="B73" s="71"/>
       <c r="C73" s="41" t="s">
         <v>155</v>
       </c>
@@ -4337,9 +4363,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="75"/>
-      <c r="B74" s="72"/>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A74" s="73"/>
+      <c r="B74" s="71"/>
       <c r="C74" s="41" t="s">
         <v>196</v>
       </c>
@@ -4351,9 +4377,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="75"/>
-      <c r="B75" s="72"/>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A75" s="73"/>
+      <c r="B75" s="71"/>
       <c r="C75" s="41" t="s">
         <v>167</v>
       </c>
@@ -4365,9 +4391,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="75"/>
-      <c r="B76" s="72"/>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A76" s="73"/>
+      <c r="B76" s="71"/>
       <c r="C76" s="41" t="s">
         <v>188</v>
       </c>
@@ -4379,19 +4405,19 @@
         <v>149</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A77" s="78"/>
-      <c r="B77" s="76"/>
+      <c r="B77" s="80"/>
       <c r="C77" s="54"/>
       <c r="D77" s="54"/>
       <c r="E77" s="55"/>
       <c r="F77" s="54"/>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="74" t="s">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A78" s="72" t="s">
         <v>72</v>
       </c>
-      <c r="B78" s="77" t="s">
+      <c r="B78" s="74" t="s">
         <v>73</v>
       </c>
       <c r="C78" s="42" t="s">
@@ -4405,9 +4431,9 @@
         <v>118</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="75"/>
-      <c r="B79" s="72"/>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A79" s="73"/>
+      <c r="B79" s="71"/>
       <c r="C79" s="41" t="s">
         <v>153</v>
       </c>
@@ -4419,17 +4445,17 @@
         <v>149</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="75"/>
-      <c r="B80" s="73"/>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A80" s="73"/>
+      <c r="B80" s="76"/>
       <c r="C80" s="50"/>
       <c r="D80" s="50"/>
       <c r="E80" s="56"/>
       <c r="F80" s="50"/>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="75"/>
-      <c r="B81" s="71" t="s">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A81" s="73"/>
+      <c r="B81" s="75" t="s">
         <v>337</v>
       </c>
       <c r="C81" s="48" t="s">
@@ -4443,9 +4469,9 @@
         <v>342</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="75"/>
-      <c r="B82" s="72"/>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A82" s="73"/>
+      <c r="B82" s="71"/>
       <c r="C82" s="41" t="s">
         <v>341</v>
       </c>
@@ -4457,17 +4483,17 @@
         <v>149</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="75"/>
-      <c r="B83" s="73"/>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A83" s="73"/>
+      <c r="B83" s="76"/>
       <c r="C83" s="50"/>
       <c r="D83" s="50"/>
       <c r="E83" s="56"/>
       <c r="F83" s="50"/>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="75"/>
-      <c r="B84" s="72" t="s">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A84" s="73"/>
+      <c r="B84" s="71" t="s">
         <v>379</v>
       </c>
       <c r="C84" s="41" t="s">
@@ -4481,9 +4507,9 @@
         <v>132</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="75"/>
-      <c r="B85" s="72"/>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A85" s="73"/>
+      <c r="B85" s="71"/>
       <c r="C85" s="41" t="s">
         <v>381</v>
       </c>
@@ -4495,14 +4521,14 @@
         <v>149</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="75"/>
-      <c r="B86" s="72"/>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A86" s="73"/>
+      <c r="B86" s="71"/>
       <c r="E86" s="44"/>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="75"/>
-      <c r="B87" s="80" t="s">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A87" s="73"/>
+      <c r="B87" s="79" t="s">
         <v>4</v>
       </c>
       <c r="C87" s="48" t="s">
@@ -4516,9 +4542,9 @@
         <v>98</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="75"/>
-      <c r="B88" s="79"/>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A88" s="73"/>
+      <c r="B88" s="77"/>
       <c r="C88" s="41" t="s">
         <v>107</v>
       </c>
@@ -4530,9 +4556,9 @@
         <v>66</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="75"/>
-      <c r="B89" s="79"/>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A89" s="73"/>
+      <c r="B89" s="77"/>
       <c r="C89" s="41" t="s">
         <v>122</v>
       </c>
@@ -4544,9 +4570,9 @@
         <v>118</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="75"/>
-      <c r="B90" s="79"/>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A90" s="73"/>
+      <c r="B90" s="77"/>
       <c r="C90" s="41" t="s">
         <v>141</v>
       </c>
@@ -4558,9 +4584,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="75"/>
-      <c r="B91" s="79"/>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A91" s="73"/>
+      <c r="B91" s="77"/>
       <c r="C91" s="41" t="s">
         <v>155</v>
       </c>
@@ -4572,9 +4598,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="75"/>
-      <c r="B92" s="79"/>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A92" s="73"/>
+      <c r="B92" s="77"/>
       <c r="C92" s="41" t="s">
         <v>161</v>
       </c>
@@ -4586,9 +4612,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="75"/>
-      <c r="B93" s="79"/>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A93" s="73"/>
+      <c r="B93" s="77"/>
       <c r="C93" s="41" t="s">
         <v>196</v>
       </c>
@@ -4600,9 +4626,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="75"/>
-      <c r="B94" s="79"/>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A94" s="73"/>
+      <c r="B94" s="77"/>
       <c r="C94" s="41" t="s">
         <v>167</v>
       </c>
@@ -4614,9 +4640,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="75"/>
-      <c r="B95" s="79"/>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A95" s="73"/>
+      <c r="B95" s="77"/>
       <c r="C95" s="41" t="s">
         <v>188</v>
       </c>
@@ -4628,13 +4654,13 @@
         <v>149</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="75"/>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A96" s="73"/>
       <c r="B96" s="82"/>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="75"/>
-      <c r="B97" s="80" t="s">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A97" s="73"/>
+      <c r="B97" s="79" t="s">
         <v>5</v>
       </c>
       <c r="C97" s="48" t="s">
@@ -4648,9 +4674,9 @@
         <v>98</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="75"/>
-      <c r="B98" s="79"/>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A98" s="73"/>
+      <c r="B98" s="77"/>
       <c r="C98" s="41" t="s">
         <v>108</v>
       </c>
@@ -4662,9 +4688,9 @@
         <v>66</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="75"/>
-      <c r="B99" s="79"/>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A99" s="73"/>
+      <c r="B99" s="77"/>
       <c r="C99" s="41" t="s">
         <v>120</v>
       </c>
@@ -4676,9 +4702,9 @@
         <v>118</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="75"/>
-      <c r="B100" s="79"/>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A100" s="73"/>
+      <c r="B100" s="77"/>
       <c r="C100" s="41" t="s">
         <v>141</v>
       </c>
@@ -4690,9 +4716,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="75"/>
-      <c r="B101" s="79"/>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A101" s="73"/>
+      <c r="B101" s="77"/>
       <c r="C101" s="41" t="s">
         <v>155</v>
       </c>
@@ -4704,9 +4730,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="75"/>
-      <c r="B102" s="79"/>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A102" s="73"/>
+      <c r="B102" s="77"/>
       <c r="C102" s="41" t="s">
         <v>161</v>
       </c>
@@ -4718,9 +4744,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="75"/>
-      <c r="B103" s="79"/>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A103" s="73"/>
+      <c r="B103" s="77"/>
       <c r="C103" s="41" t="s">
         <v>196</v>
       </c>
@@ -4732,9 +4758,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="75"/>
-      <c r="B104" s="79"/>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A104" s="73"/>
+      <c r="B104" s="77"/>
       <c r="C104" s="41" t="s">
         <v>167</v>
       </c>
@@ -4746,9 +4772,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="75"/>
-      <c r="B105" s="79"/>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A105" s="73"/>
+      <c r="B105" s="77"/>
       <c r="C105" s="41" t="s">
         <v>188</v>
       </c>
@@ -4760,15 +4786,15 @@
         <v>149</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A106" s="78"/>
       <c r="B106" s="83"/>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="74" t="s">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A107" s="72" t="s">
         <v>76</v>
       </c>
-      <c r="B107" s="77" t="s">
+      <c r="B107" s="74" t="s">
         <v>73</v>
       </c>
       <c r="C107" s="42" t="s">
@@ -4782,9 +4808,9 @@
         <v>118</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="75"/>
-      <c r="B108" s="72"/>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A108" s="73"/>
+      <c r="B108" s="71"/>
       <c r="C108" s="41" t="s">
         <v>150</v>
       </c>
@@ -4796,17 +4822,17 @@
         <v>149</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="75"/>
-      <c r="B109" s="73"/>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A109" s="73"/>
+      <c r="B109" s="76"/>
       <c r="C109" s="50"/>
       <c r="D109" s="50"/>
       <c r="E109" s="51"/>
       <c r="F109" s="50"/>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="75"/>
-      <c r="B110" s="71" t="s">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A110" s="73"/>
+      <c r="B110" s="75" t="s">
         <v>299</v>
       </c>
       <c r="C110" s="41" t="s">
@@ -4820,9 +4846,9 @@
         <v>290</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="75"/>
-      <c r="B111" s="72"/>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A111" s="73"/>
+      <c r="B111" s="71"/>
       <c r="C111" s="41" t="s">
         <v>303</v>
       </c>
@@ -4834,14 +4860,14 @@
         <v>149</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="75"/>
-      <c r="B112" s="73"/>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A112" s="73"/>
+      <c r="B112" s="76"/>
       <c r="E112" s="46"/>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="75"/>
-      <c r="B113" s="71" t="s">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A113" s="73"/>
+      <c r="B113" s="75" t="s">
         <v>79</v>
       </c>
       <c r="C113" s="48" t="s">
@@ -4855,9 +4881,9 @@
         <v>132</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="75"/>
-      <c r="B114" s="72"/>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A114" s="73"/>
+      <c r="B114" s="71"/>
       <c r="C114" s="41" t="s">
         <v>151</v>
       </c>
@@ -4869,17 +4895,17 @@
         <v>149</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="75"/>
-      <c r="B115" s="73"/>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A115" s="73"/>
+      <c r="B115" s="76"/>
       <c r="C115" s="50"/>
       <c r="D115" s="50"/>
       <c r="E115" s="51"/>
       <c r="F115" s="50"/>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="75"/>
-      <c r="B116" s="71" t="s">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A116" s="73"/>
+      <c r="B116" s="75" t="s">
         <v>258</v>
       </c>
       <c r="C116" s="41" t="s">
@@ -4893,9 +4919,9 @@
         <v>254</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="75"/>
-      <c r="B117" s="72"/>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A117" s="73"/>
+      <c r="B117" s="71"/>
       <c r="C117" s="41" t="s">
         <v>259</v>
       </c>
@@ -4907,19 +4933,19 @@
         <v>149</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A118" s="78"/>
-      <c r="B118" s="76"/>
+      <c r="B118" s="80"/>
       <c r="C118" s="54"/>
       <c r="D118" s="54"/>
       <c r="E118" s="55"/>
       <c r="F118" s="54"/>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="74" t="s">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A119" s="72" t="s">
         <v>163</v>
       </c>
-      <c r="B119" s="77" t="s">
+      <c r="B119" s="74" t="s">
         <v>13</v>
       </c>
       <c r="C119" s="42" t="s">
@@ -4933,9 +4959,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="75"/>
-      <c r="B120" s="72"/>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A120" s="73"/>
+      <c r="B120" s="71"/>
       <c r="C120" s="41" t="s">
         <v>174</v>
       </c>
@@ -4946,17 +4972,17 @@
         <v>140</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="75"/>
-      <c r="B121" s="73"/>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A121" s="73"/>
+      <c r="B121" s="76"/>
       <c r="C121" s="50"/>
       <c r="D121" s="50"/>
       <c r="E121" s="50"/>
       <c r="F121" s="50"/>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="75"/>
-      <c r="B122" s="71" t="s">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A122" s="73"/>
+      <c r="B122" s="75" t="s">
         <v>183</v>
       </c>
       <c r="C122" s="41" t="s">
@@ -4969,9 +4995,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="75"/>
-      <c r="B123" s="72"/>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A123" s="73"/>
+      <c r="B123" s="71"/>
       <c r="C123" s="41" t="s">
         <v>181</v>
       </c>
@@ -4982,9 +5008,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="75"/>
-      <c r="B124" s="72"/>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A124" s="73"/>
+      <c r="B124" s="71"/>
       <c r="C124" s="41" t="s">
         <v>177</v>
       </c>
@@ -4995,9 +5021,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="75"/>
-      <c r="B125" s="72"/>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A125" s="73"/>
+      <c r="B125" s="71"/>
       <c r="C125" s="41" t="s">
         <v>179</v>
       </c>
@@ -5008,9 +5034,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="75"/>
-      <c r="B126" s="72"/>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A126" s="73"/>
+      <c r="B126" s="71"/>
       <c r="C126" s="41" t="s">
         <v>182</v>
       </c>
@@ -5021,9 +5047,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="75"/>
-      <c r="B127" s="72"/>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A127" s="73"/>
+      <c r="B127" s="71"/>
       <c r="C127" s="41" t="s">
         <v>191</v>
       </c>
@@ -5034,13 +5060,13 @@
         <v>149</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="75"/>
-      <c r="B128" s="72"/>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="75"/>
-      <c r="B129" s="71" t="s">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A128" s="73"/>
+      <c r="B128" s="71"/>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A129" s="73"/>
+      <c r="B129" s="75" t="s">
         <v>206</v>
       </c>
       <c r="C129" s="48" t="s">
@@ -5054,9 +5080,9 @@
         <v>208</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="75"/>
-      <c r="B130" s="72"/>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A130" s="73"/>
+      <c r="B130" s="71"/>
       <c r="C130" s="41" t="s">
         <v>204</v>
       </c>
@@ -5067,9 +5093,9 @@
         <v>208</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="75"/>
-      <c r="B131" s="72"/>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A131" s="73"/>
+      <c r="B131" s="71"/>
       <c r="C131" s="41" t="s">
         <v>215</v>
       </c>
@@ -5080,9 +5106,9 @@
         <v>219</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="75"/>
-      <c r="B132" s="72"/>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A132" s="73"/>
+      <c r="B132" s="71"/>
       <c r="C132" s="41" t="s">
         <v>205</v>
       </c>
@@ -5093,9 +5119,9 @@
         <v>208</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="75"/>
-      <c r="B133" s="72"/>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A133" s="73"/>
+      <c r="B133" s="71"/>
       <c r="C133" s="41" t="s">
         <v>306</v>
       </c>
@@ -5106,9 +5132,9 @@
         <v>310</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="75"/>
-      <c r="B134" s="72"/>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A134" s="73"/>
+      <c r="B134" s="71"/>
       <c r="C134" s="41" t="s">
         <v>330</v>
       </c>
@@ -5119,9 +5145,9 @@
         <v>310</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="75"/>
-      <c r="B135" s="72"/>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A135" s="73"/>
+      <c r="B135" s="71"/>
       <c r="C135" s="41" t="s">
         <v>332</v>
       </c>
@@ -5132,9 +5158,9 @@
         <v>310</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="75"/>
-      <c r="B136" s="72"/>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A136" s="73"/>
+      <c r="B136" s="71"/>
       <c r="C136" s="41" t="s">
         <v>217</v>
       </c>
@@ -5145,9 +5171,9 @@
         <v>218</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="75"/>
-      <c r="B137" s="72"/>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A137" s="73"/>
+      <c r="B137" s="71"/>
       <c r="C137" s="41" t="s">
         <v>221</v>
       </c>
@@ -5158,9 +5184,9 @@
         <v>212</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="75"/>
-      <c r="B138" s="72"/>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A138" s="73"/>
+      <c r="B138" s="71"/>
       <c r="C138" s="41" t="s">
         <v>202</v>
       </c>
@@ -5171,9 +5197,9 @@
         <v>212</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="75"/>
-      <c r="B139" s="72"/>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A139" s="73"/>
+      <c r="B139" s="71"/>
       <c r="C139" s="41" t="s">
         <v>262</v>
       </c>
@@ -5184,9 +5210,9 @@
         <v>212</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="75"/>
-      <c r="B140" s="72"/>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A140" s="73"/>
+      <c r="B140" s="71"/>
       <c r="C140" s="41" t="s">
         <v>264</v>
       </c>
@@ -5197,13 +5223,13 @@
         <v>213</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="75"/>
-      <c r="B141" s="72"/>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="75"/>
-      <c r="B142" s="71" t="s">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A141" s="73"/>
+      <c r="B141" s="71"/>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A142" s="73"/>
+      <c r="B142" s="75" t="s">
         <v>222</v>
       </c>
       <c r="C142" s="48" t="s">
@@ -5217,9 +5243,9 @@
         <v>208</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="75"/>
-      <c r="B143" s="72"/>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A143" s="73"/>
+      <c r="B143" s="71"/>
       <c r="C143" s="41" t="s">
         <v>308</v>
       </c>
@@ -5230,9 +5256,9 @@
         <v>310</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="75"/>
-      <c r="B144" s="72"/>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A144" s="73"/>
+      <c r="B144" s="71"/>
       <c r="C144" s="41" t="s">
         <v>225</v>
       </c>
@@ -5243,9 +5269,9 @@
         <v>212</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A145" s="75"/>
-      <c r="B145" s="72"/>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A145" s="73"/>
+      <c r="B145" s="71"/>
       <c r="C145" s="41" t="s">
         <v>265</v>
       </c>
@@ -5256,9 +5282,9 @@
         <v>212</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A146" s="75"/>
-      <c r="B146" s="72"/>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A146" s="73"/>
+      <c r="B146" s="71"/>
       <c r="C146" s="41" t="s">
         <v>267</v>
       </c>
@@ -5269,13 +5295,13 @@
         <v>213</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A147" s="75"/>
-      <c r="B147" s="73"/>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A148" s="75"/>
-      <c r="B148" s="71" t="s">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A147" s="73"/>
+      <c r="B147" s="76"/>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A148" s="73"/>
+      <c r="B148" s="75" t="s">
         <v>384</v>
       </c>
       <c r="C148" s="48" t="s">
@@ -5289,9 +5315,9 @@
         <v>271</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A149" s="75"/>
-      <c r="B149" s="72"/>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A149" s="73"/>
+      <c r="B149" s="71"/>
       <c r="C149" s="41" t="s">
         <v>387</v>
       </c>
@@ -5304,6 +5330,17 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="B148:B149"/>
+    <mergeCell ref="B142:B147"/>
+    <mergeCell ref="A119:A149"/>
+    <mergeCell ref="B116:B118"/>
+    <mergeCell ref="B122:B128"/>
+    <mergeCell ref="B129:B141"/>
+    <mergeCell ref="B119:B121"/>
+    <mergeCell ref="A107:A118"/>
+    <mergeCell ref="B113:B115"/>
+    <mergeCell ref="B107:B109"/>
+    <mergeCell ref="B110:B112"/>
     <mergeCell ref="B84:B86"/>
     <mergeCell ref="A2:A45"/>
     <mergeCell ref="B2:B11"/>
@@ -5319,17 +5356,6 @@
     <mergeCell ref="B97:B106"/>
     <mergeCell ref="B78:B80"/>
     <mergeCell ref="B81:B83"/>
-    <mergeCell ref="B148:B149"/>
-    <mergeCell ref="B142:B147"/>
-    <mergeCell ref="A119:A149"/>
-    <mergeCell ref="B116:B118"/>
-    <mergeCell ref="B122:B128"/>
-    <mergeCell ref="B129:B141"/>
-    <mergeCell ref="B119:B121"/>
-    <mergeCell ref="A107:A118"/>
-    <mergeCell ref="B113:B115"/>
-    <mergeCell ref="B107:B109"/>
-    <mergeCell ref="B110:B112"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
